--- a/static/data/exports/Retro_GA_AE_2017.xlsx
+++ b/static/data/exports/Retro_GA_AE_2017.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,8 +576,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>53</v>
+      </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>29</v>
@@ -638,6 +651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>60</v>
+      </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
@@ -700,6 +726,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>69</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>53</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>49</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>70</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1088,19 @@
           <t>BMUP</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>50</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1163,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>63</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>62</v>
+      </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
@@ -1196,6 +1313,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>43</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1450,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>40</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1525,19 @@
           <t>GVP</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>48</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1600,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>45</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1675,19 @@
           <t>BMUP</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>37</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1750,19 @@
           <t>GoPrP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>40</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1825,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>53</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1900,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>51</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1975,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>50</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2050,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>33</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2125,19 @@
           <t>GoPrP</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>70</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2262,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>54</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2337,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>45</v>
+      </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
@@ -2126,6 +2412,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>53</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2487,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>42</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2624,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>62</v>
+      </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
@@ -2374,6 +2699,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>59</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2774,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>44</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2849,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>33</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2924,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>62</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3061,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>52</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3136,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>27</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3211,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>54</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3286,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>60</v>
+      </c>
       <c r="Q39" t="b">
         <v>1</v>
       </c>
@@ -2932,6 +3361,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>34</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3436,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>45</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3511,19 @@
           <t>GSM</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>60</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3586,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>33</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3723,19 @@
           <t>BMUP</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>50</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3798,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>36</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3873,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>42</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3948,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
       <c r="Q48" t="b">
         <v>1</v>
       </c>
@@ -3490,6 +4023,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>54</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4098,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>56</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4173,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>45</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3738,8 +4310,21 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>53</v>
+      </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>29</v>
@@ -3800,6 +4385,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>40</v>
+      </c>
       <c r="Q54" t="b">
         <v>1</v>
       </c>
@@ -3862,6 +4460,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>56</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4535,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>34</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4672,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>42</v>
+      </c>
       <c r="Q58" t="b">
         <v>1</v>
       </c>
@@ -4110,6 +4747,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>43</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4822,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>45</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4897,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>46</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5034,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>51</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5109,19 @@
           <t>SaJPCs</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>47</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5184,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>54</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5259,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>49</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5334,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>49</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5409,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>38</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5484,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>58</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5621,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>30</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5696,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>41</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5771,19 @@
           <t>UGP</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>54</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5846,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>40</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5921,19 @@
           <t>GSM</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>32</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6058,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>50</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6133,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>53</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6208,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>38</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6283,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>46</v>
+      </c>
       <c r="Q80" t="b">
         <v>1</v>
       </c>
@@ -5474,8 +6358,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>38</v>
+      </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>29</v>
@@ -5536,6 +6433,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>34</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6570,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>37</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6645,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>51</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6720,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>49</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,8 +6795,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>55</v>
+      </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>29</v>
@@ -5908,6 +6870,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>43</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +6945,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>47</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6094,6 +7082,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>46</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,8 +7157,21 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>53</v>
+      </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>29</v>
@@ -6218,6 +7232,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>47</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,8 +7307,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>43</v>
+      </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>29</v>
@@ -6342,8 +7382,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>48</v>
+      </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>29</v>
@@ -6404,6 +7457,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>50</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7532,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>47</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7607,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>45</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7682,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>31</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7757,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>40</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7894,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>65</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +7969,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>30</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8044,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>54</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8119,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>30</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8194,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>53</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8269,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>37</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8344,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>54</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8419,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>43</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8494,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>45</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8631,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>50</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8706,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>43</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8781,19 @@
           <t>GSM</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>50</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8856,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>39</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +8931,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>50</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9068,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>46</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,8 +9143,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>34</v>
+      </c>
       <c r="Q119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>29</v>
@@ -7892,6 +9218,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>57</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9293,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>43</v>
+      </c>
       <c r="Q121" t="b">
         <v>1</v>
       </c>
@@ -8016,6 +9368,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>41</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9443,19 @@
           <t>GSM</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>65</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9518,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>53</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,6 +9593,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>41</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9730,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>43</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +9805,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>46</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9880,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>78</v>
+      </c>
       <c r="Q129" t="b">
         <v>1</v>
       </c>
@@ -8512,8 +9955,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>44</v>
+      </c>
       <c r="Q130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>29</v>
@@ -8636,6 +10092,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>53</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10167,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>48</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10242,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>42</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10317,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>45</v>
+      </c>
       <c r="Q135" t="b">
         <v>1</v>
       </c>
@@ -8884,8 +10392,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>55</v>
+      </c>
       <c r="Q136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>29</v>
@@ -8946,6 +10467,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>41</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10542,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>36</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9132,8 +10679,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>45</v>
+      </c>
       <c r="Q140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>29</v>
@@ -9194,6 +10754,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>58</v>
+      </c>
       <c r="Q141" t="b">
         <v>1</v>
       </c>
@@ -9256,6 +10829,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>64</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +10966,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>42</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,8 +11041,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>70</v>
+      </c>
       <c r="Q145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>29</v>
@@ -9504,6 +11116,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>56</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11191,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>42</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11266,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>60</v>
+      </c>
       <c r="Q148" t="b">
         <v>1</v>
       </c>
@@ -9690,6 +11341,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>37</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9814,8 +11478,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>64</v>
+      </c>
       <c r="Q151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>29</v>
@@ -9876,6 +11553,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>58</v>
+      </c>
       <c r="Q152" t="b">
         <v>1</v>
       </c>
@@ -9938,6 +11628,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>45</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11703,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>42</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +11778,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>35</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +11915,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>39</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +11990,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>60</v>
+      </c>
       <c r="Q158" t="b">
         <v>1</v>
       </c>
@@ -10310,6 +12065,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>51</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12140,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>40</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12215,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>32</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12352,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>49</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12427,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>54</v>
+      </c>
       <c r="Q164" t="b">
         <v>1</v>
       </c>
@@ -10682,8 +12502,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>41</v>
+      </c>
       <c r="Q165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>29</v>
@@ -10744,6 +12577,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>53</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +12714,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>39</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12789,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>35</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +12864,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>37</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +12939,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>53</v>
+      </c>
       <c r="Q171" t="b">
         <v>1</v>
       </c>
@@ -11116,6 +13014,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>46</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,8 +13089,21 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>60</v>
+      </c>
       <c r="Q173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>29</v>
@@ -11240,6 +13164,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>45</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13239,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>62</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13314,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>47</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>68</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13526,19 @@
           <t>NGRF</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>49</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13601,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>57</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,8 +13676,21 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>40</v>
+      </c>
       <c r="Q181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>29</v>
@@ -11736,6 +13751,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>53</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13826,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>47</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +13901,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>47</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +14038,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>34</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,6 +14113,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>61</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12108,6 +14188,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>30</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14263,19 @@
           <t>NGRF</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>35</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14338,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>64</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14413,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>52</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14488,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>38</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,8 +14563,21 @@
           <t>GVP</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>56</v>
+      </c>
       <c r="Q193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>29</v>
@@ -12480,6 +14638,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>30</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14713,19 @@
           <t>UGP</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>54</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14788,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>40</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12728,6 +14925,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>41</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +15000,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>41</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +15075,19 @@
           <t>GoPrP</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>42</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15150,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>49</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12976,6 +15225,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>52</v>
+      </c>
       <c r="Q202" t="b">
         <v>0</v>
       </c>
@@ -13038,6 +15300,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>63</v>
+      </c>
       <c r="Q203" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15375,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>58</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15450,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>58</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15587,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>47</v>
+      </c>
       <c r="Q207" t="b">
         <v>1</v>
       </c>
@@ -13348,6 +15662,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>53</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +15737,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>38</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15874,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>50</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +15949,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>56</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,6 +16024,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>46</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,8 +16099,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>45</v>
+      </c>
       <c r="Q214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
         <v>29</v>
@@ -13782,6 +16174,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>48</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16249,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>41</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16386,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>42</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16461,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>41</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,6 +16536,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>62</v>
+      </c>
       <c r="Q220" t="b">
         <v>1</v>
       </c>
@@ -14154,6 +16611,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>39</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16686,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>64</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +16823,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>43</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +16898,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>67</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +16973,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>37</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,6 +17048,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>57</v>
+      </c>
       <c r="Q227" t="b">
         <v>0</v>
       </c>
@@ -14588,6 +17123,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>45</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17198,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>40</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17273,19 @@
           <t>GVP</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>48</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17348,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>61</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14898,6 +17485,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>65</v>
+      </c>
       <c r="Q233" t="b">
         <v>0</v>
       </c>
@@ -14960,6 +17560,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>50</v>
+      </c>
       <c r="Q234" t="b">
         <v>1</v>
       </c>
@@ -15022,6 +17635,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>48</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17710,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>48</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17785,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>48</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +17860,19 @@
           <t>GVP</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>60</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15270,6 +17935,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>50</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18072,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>46</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +18147,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>60</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15518,6 +18222,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>63</v>
+      </c>
       <c r="Q243" t="b">
         <v>1</v>
       </c>
@@ -15580,6 +18297,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>54</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18372,19 @@
           <t>GVP</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>38</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18447,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>44</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18584,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>49</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,8 +18659,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>54</v>
+      </c>
       <c r="Q249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
         <v>29</v>
@@ -15952,6 +18734,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>50</v>
+      </c>
       <c r="Q250" t="b">
         <v>1</v>
       </c>
@@ -16014,6 +18809,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>47</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16076,6 +18884,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>43</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16138,6 +18959,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>53</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +19034,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>42</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16324,6 +19171,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>40</v>
+      </c>
       <c r="Q256" t="b">
         <v>0</v>
       </c>
@@ -16386,6 +19246,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>45</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16448,6 +19321,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>47</v>
+      </c>
       <c r="Q258" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19396,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>70</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19471,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>49</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19546,19 @@
           <t>APoI</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>35</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19621,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>45</v>
+      </c>
       <c r="Q262" t="b">
         <v>1</v>
       </c>
@@ -16758,6 +19696,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>63</v>
+      </c>
       <c r="Q263" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +19771,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>46</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +19908,19 @@
           <t>GSRP</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>47</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17006,6 +19983,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>32</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,6 +20058,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>44</v>
+      </c>
       <c r="Q268" t="b">
         <v>1</v>
       </c>
@@ -17130,6 +20133,19 @@
           <t>GSM</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>50</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20208,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>68</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20283,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>51</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20420,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>43</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17440,6 +20495,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>58</v>
+      </c>
       <c r="Q274" t="b">
         <v>1</v>
       </c>
@@ -17502,6 +20570,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>57</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +20707,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>52</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,8 +20782,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>40</v>
+      </c>
       <c r="Q278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
         <v>29</v>
@@ -17750,6 +20857,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>50</v>
+      </c>
       <c r="Q279" t="b">
         <v>1</v>
       </c>
@@ -17812,6 +20932,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>37</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +21007,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>40</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +21082,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>28</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21157,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>55</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21294,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>39</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18184,6 +21369,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>32</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18246,8 +21444,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>65</v>
+      </c>
       <c r="Q287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
         <v>29</v>
@@ -18308,6 +21519,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>54</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21594,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>48</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,6 +21669,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>40</v>
+      </c>
       <c r="Q290" t="b">
         <v>0</v>
       </c>
@@ -18493,6 +21743,19 @@
         <is>
           <t>MAG</t>
         </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>33</v>
       </c>
       <c r="Q291" t="b">
         <v>0</v>
